--- a/Figure 2/Figure 2-K.xlsx
+++ b/Figure 2/Figure 2-K.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Wench\Desktop\英文写作\英文写作\工程菌KR32\论文需要上传的数据\iMetaOmics20260210\Figure 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4166D976-1A0A-4CC2-A07E-1B1880B756C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D1CED39-9A5C-4DB1-A50D-B88FA28B4CF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22220" yWindow="2300" windowWidth="15760" windowHeight="15580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28790" yWindow="4080" windowWidth="16730" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -122,7 +122,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -142,6 +142,12 @@
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -164,13 +170,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -457,235 +466,236 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20.6640625" customWidth="1"/>
-    <col min="2" max="2" width="12.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="12.25" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="2"/>
+      <c r="B1" s="3" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2" s="4">
         <v>8.4180208000831414</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>13.684851274209233</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4" s="4">
         <v>14.386353007549495</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>9.828447565529169</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6" s="4">
         <v>8.2584198766247745</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="4">
         <v>12.693840889014261</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8" s="4">
         <v>15.254878963113629</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9" s="4">
         <v>13.725679417419512</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10" s="4">
         <v>9.7319446815776001</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="3">
+      <c r="B11" s="4">
         <v>14.289850123597926</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="3">
+      <c r="B12" s="4">
         <v>10.7600715606001</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="3">
+      <c r="B13" s="4">
         <v>14.497702489032076</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="3">
+      <c r="B14" s="4">
         <v>15.39592163965823</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15" s="4">
         <v>14.805769387800552</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B16" s="3">
+      <c r="B16" s="4">
         <v>15.061873195210488</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B17" s="3">
+      <c r="B17" s="4">
         <v>9.4275894321918781</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3">
+      <c r="B18" s="4">
         <v>8.4625605926761747</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19" s="4">
         <v>7.5680530914327715</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20" s="4">
         <v>15.1472411310138</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21" s="4">
         <v>13.521538701368117</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22" s="4">
         <v>11.112678251961608</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23" s="4">
         <v>12.697552538397012</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24" s="4">
         <v>9.3533564445368249</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25" s="4">
         <v>14.508837437180333</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="3">
+      <c r="B26" s="4">
         <v>8.5219469828002197</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="3">
+      <c r="B27" s="4">
         <v>12.434025432221569</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B28" s="4">
         <v>11.906971219870686</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="4">
         <v>10.904825886527455</v>
       </c>
     </row>
